--- a/Data/Rehires/Workday_Rehire_Slovakia_Regression_PK17.xlsx
+++ b/Data/Rehires/Workday_Rehire_Slovakia_Regression_PK17.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="76">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -232,22 +232,19 @@
     <t>Auto 43240260</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Kiel Krajcik' Employee:{10699808}TimeoutError: locator.click: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for locator('//label[contains(.,\'Hire Date\')]/parent::div/following-sibling::div/descendant::input[@data-automation-id=\'dateSectionDay-input\']')[22m
-</t>
-  </si>
-  <si>
-    <t>10699808</t>
-  </si>
-  <si>
-    <t>Kiel</t>
-  </si>
-  <si>
-    <t>Krajcik</t>
-  </si>
-  <si>
-    <t>Auto 54710167</t>
+    <t>Test_3</t>
+  </si>
+  <si>
+    <t>10699804</t>
+  </si>
+  <si>
+    <t>Mathilde</t>
+  </si>
+  <si>
+    <t>Dietrich</t>
+  </si>
+  <si>
+    <t>Auto 26606994</t>
   </si>
 </sst>
 </file>
@@ -331,7 +328,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -957,7 +954,7 @@
       </c>
       <c r="J2" s="13">
         <f>TODAY()-1</f>
-        <v>45827</v>
+        <v>45830</v>
       </c>
       <c r="K2" s="14" t="s">
         <v>48</v>
@@ -1012,7 +1009,7 @@
       </c>
       <c r="AB2" s="13">
         <f>J2</f>
-        <v>45827</v>
+        <v>45830</v>
       </c>
       <c r="AC2" s="12" t="s">
         <v>61</v>
@@ -1035,14 +1032,14 @@
       </c>
       <c r="AI2" s="21">
         <f>TODAY()-29</f>
-        <v>45799</v>
+        <v>45802</v>
       </c>
       <c r="AJ2" s="21" t="s">
         <v>41</v>
       </c>
       <c r="AK2" s="21">
         <f>TODAY()-30</f>
-        <v>45798</v>
+        <v>45801</v>
       </c>
       <c r="AL2" s="22" t="s">
         <v>41</v>
@@ -1085,7 +1082,7 @@
       </c>
       <c r="J3" s="13">
         <f>TODAY()-1</f>
-        <v>45827</v>
+        <v>45830</v>
       </c>
       <c r="K3" s="14" t="s">
         <v>48</v>
@@ -1140,7 +1137,7 @@
       </c>
       <c r="AB3" s="13">
         <f>J3</f>
-        <v>45827</v>
+        <v>45830</v>
       </c>
       <c r="AC3" s="12" t="s">
         <v>61</v>
@@ -1163,14 +1160,14 @@
       </c>
       <c r="AI3" s="21">
         <f>TODAY()-29</f>
-        <v>45799</v>
+        <v>45802</v>
       </c>
       <c r="AJ3" s="21" t="s">
         <v>41</v>
       </c>
       <c r="AK3" s="21">
         <f>TODAY()-30</f>
-        <v>45798</v>
+        <v>45801</v>
       </c>
       <c r="AL3" s="22" t="s">
         <v>41</v>
@@ -1182,12 +1179,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" ht="15.65" customHeight="1" spans="2:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="1" t="s">
+    <row r="4" ht="15.65" customHeight="1" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>71</v>
       </c>
+      <c r="B4" s="23" t="s">
+        <v>41</v>
+      </c>
       <c r="C4" s="7" t="s">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>43</v>
@@ -1206,11 +1206,11 @@
       </c>
       <c r="I4" s="12" t="str">
         <f>F4&amp;" "&amp;G4</f>
-        <v>Kiel Krajcik</v>
+        <v>Mathilde Dietrich</v>
       </c>
       <c r="J4" s="13">
         <f>TODAY()-1</f>
-        <v>45827</v>
+        <v>45830</v>
       </c>
       <c r="K4" s="14" t="s">
         <v>48</v>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="AB4" s="13">
         <f>J4</f>
-        <v>45827</v>
+        <v>45830</v>
       </c>
       <c r="AC4" s="12" t="s">
         <v>61</v>
@@ -1288,14 +1288,14 @@
       </c>
       <c r="AI4" s="21">
         <f>TODAY()-29</f>
-        <v>45799</v>
+        <v>45802</v>
       </c>
       <c r="AJ4" s="21" t="s">
         <v>41</v>
       </c>
       <c r="AK4" s="21">
         <f>TODAY()-30</f>
-        <v>45798</v>
+        <v>45801</v>
       </c>
       <c r="AL4" s="22" t="s">
         <v>41</v>
